--- a/artfynd/A 53680-2024 artfynd.xlsx
+++ b/artfynd/A 53680-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117814335</v>
       </c>
       <c r="B2" t="n">
-        <v>98267</v>
+        <v>98275</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53680-2024 artfynd.xlsx
+++ b/artfynd/A 53680-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117814335</v>
       </c>
       <c r="B2" t="n">
-        <v>98275</v>
+        <v>98277</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53680-2024 artfynd.xlsx
+++ b/artfynd/A 53680-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117814335</v>
       </c>
       <c r="B2" t="n">
-        <v>98277</v>
+        <v>98285</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53680-2024 artfynd.xlsx
+++ b/artfynd/A 53680-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117814335</v>
       </c>
       <c r="B2" t="n">
-        <v>98285</v>
+        <v>98288</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53680-2024 artfynd.xlsx
+++ b/artfynd/A 53680-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117814335</v>
       </c>
       <c r="B2" t="n">
-        <v>98288</v>
+        <v>98290</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53680-2024 artfynd.xlsx
+++ b/artfynd/A 53680-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117814335</v>
       </c>
       <c r="B2" t="n">
-        <v>98290</v>
+        <v>98296</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
